--- a/packing.xlsx
+++ b/packing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leo\Desktop\line bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F1E19C7-560C-4BBA-9E19-F55D83464BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A737974-42E9-4E99-8A66-E0C9662A4EB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{4A3EA58E-B165-454C-AC0F-C59F5CA2A667}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
   <si>
     <t>company</t>
   </si>
@@ -74,14 +74,74 @@
     <t>surasart.m@vprompt.co.th</t>
   </si>
   <si>
-    <t>090-896-5279</t>
+    <t>CH. SIRI PACKING (BT Pack)</t>
+  </si>
+  <si>
+    <t>K.เบิ้ม</t>
+  </si>
+  <si>
+    <t>Wood crates, Pallet</t>
+  </si>
+  <si>
+    <t>082-540-0444</t>
+  </si>
+  <si>
+    <t>090-896-5280</t>
+  </si>
+  <si>
+    <t>bermy_k@hotmail.com</t>
+  </si>
+  <si>
+    <t>SGT Service (Thailand) Co., Ltd.</t>
+  </si>
+  <si>
+    <t>K. หนิง</t>
+  </si>
+  <si>
+    <t>Fumigation</t>
+  </si>
+  <si>
+    <t>061-4636-536</t>
+  </si>
+  <si>
+    <t>sale_service@sgtthailand.com</t>
+  </si>
+  <si>
+    <t>Sakulperm Inter and Service</t>
+  </si>
+  <si>
+    <t>K. รุ้ง</t>
+  </si>
+  <si>
+    <t>Labor</t>
+  </si>
+  <si>
+    <t>098-376-9698</t>
+  </si>
+  <si>
+    <t>sakulperm.co@gmail.com</t>
+  </si>
+  <si>
+    <t>Triple J Relocation Service</t>
+  </si>
+  <si>
+    <t>K. Wut</t>
+  </si>
+  <si>
+    <t>Bangna</t>
+  </si>
+  <si>
+    <t>worawut@triplejrelocation.com</t>
+  </si>
+  <si>
+    <t>081-931-9172</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -100,6 +160,12 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -467,14 +533,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BFEFA47-423B-41EB-BA65-A404FF8175BF}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="34.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -504,11 +571,11 @@
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -517,9 +584,85 @@
         <v>8</v>
       </c>
     </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{51629A5B-C3C2-414B-AC24-0BC623C7899D}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{35BBEF75-2795-441F-B152-BC84E2068938}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{2573010A-8D38-4229-8823-03496925E1D6}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{0E5501BC-99B3-4969-AB45-94333FE9C8E9}"/>
+    <hyperlink ref="C5" r:id="rId4" xr:uid="{00824FE2-B054-4338-9D00-1D7772F3E56A}"/>
+    <hyperlink ref="C6" r:id="rId5" xr:uid="{FC9F6F5C-1D33-4F2A-AB05-5CF1797EAB74}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
